--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486513_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486513_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2631</v>
+        <v>2.7547</v>
       </c>
       <c r="E2" t="n">
-        <v>2.581</v>
+        <v>2.8416</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6821</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0985</v>
+        <v>-0.4452</v>
       </c>
       <c r="H2" t="n">
-        <v>2.348</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2494</v>
+        <v>-1.2359</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4524</v>
+        <v>1.2546</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2994</v>
+        <v>1.7702</v>
       </c>
       <c r="L2" t="n">
-        <v>0.153</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3539</v>
+        <v>-1.6998</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0486</v>
+        <v>-0.9794</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4024</v>
+        <v>-0.7204</v>
       </c>
       <c r="P2" t="n">
         <v>-0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9678</v>
+        <v>0.4179</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2161</v>
+        <v>0.6321</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7516</v>
+        <v>-0.2142</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5857</v>
+        <v>2.9995</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5857</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0339</v>
+        <v>2.4554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1517</v>
+        <v>5.2255</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1178</v>
+        <v>-2.7702</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4452</v>
+        <v>-0.1431</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7907999999999999</v>
+        <v>-1.7672</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2359</v>
+        <v>1.624</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2546</v>
+        <v>2.5385</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7702</v>
+        <v>0.2587</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5155999999999999</v>
+        <v>2.2799</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6998</v>
+        <v>-2.6817</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9794</v>
+        <v>-2.0258</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7204</v>
+        <v>-0.6558</v>
       </c>
       <c r="P3" t="n">
+        <v>1.7401</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.2728</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9421</v>
+        <v>0.0589</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.245</v>
+        <v>0.2139</v>
       </c>
       <c r="V3" t="n">
-        <v>2.9995</v>
+        <v>0.5857</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2599</v>
+        <v>2.8456</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7395</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4809</v>
+        <v>2.087</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5626</v>
+        <v>1.8672</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0818</v>
+        <v>0.2198</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9132</v>
+        <v>2.0985</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.082</v>
+        <v>2.348</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.2494</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1381</v>
+        <v>2.4524</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3348</v>
+        <v>2.2994</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8032</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0512</v>
+        <v>-0.3539</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4169</v>
+        <v>0.0486</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6344</v>
+        <v>-0.4024</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.87</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.305</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.1751</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.394</v>
+        <v>0.7916</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5997</v>
+        <v>0.5023</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2056</v>
+        <v>0.2893</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>-0.5857</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.066</v>
+        <v>1.4482</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0827</v>
+        <v>1.2526</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0167</v>
+        <v>0.1956</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1431</v>
+        <v>-0.9132</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7672</v>
+        <v>-0.082</v>
       </c>
       <c r="I5" t="n">
-        <v>1.624</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5385</v>
+        <v>1.1381</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2587</v>
+        <v>0.3348</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2799</v>
+        <v>0.8032</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6817</v>
+        <v>-2.0512</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6558</v>
+        <v>-1.6344</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1166</v>
+        <v>0.3614</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0839</v>
+        <v>0.2896</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0327</v>
+        <v>0.0718</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5857</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8456</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.361</v>
+        <v>0.9767</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3127</v>
+        <v>1.0517</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0483</v>
+        <v>-0.075</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0205</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1183</v>
+        <v>0.4975</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5547</v>
+        <v>0.4314</v>
       </c>
       <c r="V6" t="n">
         <v>0.9347</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3092</v>
+        <v>-0.1221</v>
       </c>
       <c r="E8" t="n">
-        <v>1.077</v>
+        <v>1.3257</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3861</v>
+        <v>-1.4478</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1534</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0394</v>
+        <v>0.2265</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1454</v>
+        <v>0.1034</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1848</v>
+        <v>0.1232</v>
       </c>
       <c r="V8" t="n">
         <v>0.9347</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2374</v>
+        <v>-2.8398</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7611</v>
+        <v>0.4321</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.9985</v>
+        <v>-3.2719</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2942</v>
+        <v>-0.2649</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0766</v>
+        <v>-1.022</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2176</v>
+        <v>0.757</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7851</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5173</v>
+        <v>0.073</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2677</v>
+        <v>0.4789</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0792</v>
+        <v>-0.8169</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5939</v>
+        <v>-1.095</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4854</v>
+        <v>0.2781</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5225</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1443</v>
+        <v>-0.0321</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6307</v>
+        <v>-0.1622</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.1301</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.8902</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0854</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9892</v>
+        <v>-3.2202</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2519</v>
+        <v>-2.5468</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2411</v>
+        <v>-0.6735</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2649</v>
+        <v>-2.2648</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.022</v>
+        <v>-1.6728</v>
       </c>
       <c r="I10" t="n">
-        <v>0.757</v>
+        <v>-0.5921</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5518999999999999</v>
+        <v>-0.749</v>
       </c>
       <c r="K10" t="n">
-        <v>0.073</v>
+        <v>0.1857</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4789</v>
+        <v>-0.9347</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8169</v>
+        <v>-1.5158</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.095</v>
+        <v>-1.8584</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2781</v>
+        <v>0.3426</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6525</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R10" t="n">
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1816</v>
+        <v>0.6324</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3425</v>
+        <v>0.5948</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1609</v>
+        <v>0.0375</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8902</v>
+        <v>0.3698</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0202</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4929</v>
+        <v>-3.5832</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.727</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7659</v>
+        <v>-4.1835</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2648</v>
+        <v>-2.2942</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6728</v>
+        <v>-1.0766</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5921</v>
+        <v>-1.2176</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.749</v>
+        <v>0.7851</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1857</v>
+        <v>0.5173</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9347</v>
+        <v>0.2677</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5158</v>
+        <v>-3.0792</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8584</v>
+        <v>-1.5939</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3426</v>
+        <v>-1.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9576</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3597</v>
+        <v>0.7985</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4146</v>
+        <v>0.4699</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0549</v>
+        <v>0.3287</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3698</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7187</v>
+        <v>-6.4719</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0914</v>
+        <v>-4.0603</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6273</v>
+        <v>-2.4116</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1911</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1372</v>
+        <v>0.1097</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.2896</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3957</v>
+        <v>-0.18</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6504</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.461999999999999</v>
+        <v>-6.434699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.893799999999999</v>
+        <v>7.921100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.3558</v>
+        <v>-14.3561</v>
       </c>
       <c r="G13" t="n">
         <v>-8.4429</v>
@@ -1447,7 +1447,7 @@
         <v>4.578999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>4.6458</v>
+        <v>4.645799999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-17.6678</v>
@@ -1456,7 +1456,7 @@
         <v>-10.464</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.2039</v>
+        <v>-7.203900000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-3.2626</v>
@@ -1468,16 +1468,16 @@
         <v>11.9628</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9801</v>
+        <v>4.007700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7486</v>
+        <v>2.776</v>
       </c>
       <c r="U13" t="n">
         <v>1.2317</v>
       </c>
       <c r="V13" t="n">
-        <v>1.263100000000001</v>
+        <v>1.2631</v>
       </c>
       <c r="W13" t="n">
         <v>11.1459</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8013</v>
+        <v>3.7769</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2736</v>
+        <v>3.1618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="G14" t="n">
         <v>3.0046</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0331</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0601</v>
+        <v>-0.0517</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0688</v>
+        <v>0.0186</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9347</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4415</v>
+        <v>2.3936</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1249</v>
+        <v>3.7868</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3166</v>
+        <v>-1.3931</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6192</v>
+        <v>0.3837</v>
       </c>
       <c r="H15" t="n">
-        <v>0.961</v>
+        <v>0.9033</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3419</v>
+        <v>-0.5195</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0544</v>
+        <v>1.8525</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8249</v>
+        <v>1.3536</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2295</v>
+        <v>0.4989</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4353</v>
+        <v>-1.4688</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8639</v>
+        <v>-0.4504</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5714</v>
+        <v>-1.0184</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0616</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1454</v>
+        <v>-0.3256</v>
       </c>
       <c r="U15" t="n">
-        <v>0.207</v>
+        <v>-0.317</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0207</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2159</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1406</v>
+        <v>2.114</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8985</v>
+        <v>2.0132</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7579</v>
+        <v>0.1008</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3837</v>
+        <v>0.6192</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9033</v>
+        <v>0.961</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5195</v>
+        <v>-0.3419</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8525</v>
+        <v>2.0544</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3536</v>
+        <v>1.8249</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4989</v>
+        <v>0.2295</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4688</v>
+        <v>-1.4353</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4504</v>
+        <v>-0.8639</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0184</v>
+        <v>-0.5714</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8956</v>
+        <v>-0.2659</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2139</v>
+        <v>-0.2572</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6817</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0.0207</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>0.2159</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.47</v>
+        <v>1.2685</v>
       </c>
       <c r="E17" t="n">
-        <v>1.771</v>
+        <v>1.6822</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3009</v>
+        <v>-0.4137</v>
       </c>
       <c r="G17" t="n">
-        <v>0.881</v>
+        <v>-0.3632</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3072</v>
+        <v>0.1125</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5737</v>
+        <v>-0.4757</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3497</v>
+        <v>1.955</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3536</v>
+        <v>0.8609</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9961</v>
+        <v>1.0941</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4688</v>
+        <v>-2.3182</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0464</v>
+        <v>-0.7484</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4224</v>
+        <v>-1.5698</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0189</v>
+        <v>-0.3233</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0769</v>
+        <v>-0.4002</v>
       </c>
       <c r="U17" t="n">
-        <v>0.058</v>
+        <v>0.0769</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3904</v>
+        <v>2.8249</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5857</v>
+        <v>3.3899</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4651</v>
+        <v>1.1425</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3115</v>
+        <v>1.6592</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1537</v>
+        <v>-0.5167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7867</v>
+        <v>0.881</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9915</v>
+        <v>0.3072</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2048</v>
+        <v>0.5737</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1964</v>
+        <v>2.3497</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0434</v>
+        <v>1.3536</v>
       </c>
       <c r="L18" t="n">
-        <v>0.153</v>
+        <v>0.9961</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4097</v>
+        <v>-1.4688</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0519</v>
+        <v>-1.0464</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3578</v>
+        <v>-0.4224</v>
       </c>
       <c r="P18" t="n">
         <v>0.2175</v>
@@ -1858,28 +1858,28 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2005</v>
+        <v>-0.3464</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9421</v>
+        <v>-0.1887</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2584</v>
+        <v>-0.1577</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7395</v>
+        <v>0.3904</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7395</v>
+        <v>0.5857</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7097</v>
+        <v>0.889</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1234</v>
+        <v>0.1006</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4137</v>
+        <v>0.7884</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3632</v>
+        <v>-0.1545</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1125</v>
+        <v>-0.5537</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4757</v>
+        <v>0.3992</v>
       </c>
       <c r="J19" t="n">
-        <v>1.955</v>
+        <v>0.5692</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8609</v>
+        <v>0.4927</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0941</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3182</v>
+        <v>-0.7237</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7484</v>
+        <v>-1.0464</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5698</v>
+        <v>0.3227</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.882</v>
+        <v>-0.7411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9589</v>
+        <v>-0.4687</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0769</v>
+        <v>-0.2725</v>
       </c>
       <c r="V19" t="n">
-        <v>2.8249</v>
+        <v>-0.3904</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1145</v>
+        <v>0.6354</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4582</v>
+        <v>-0.3591</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5727</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1545</v>
+        <v>0.7867</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5537</v>
+        <v>0.9915</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3992</v>
+        <v>-0.2048</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5692</v>
+        <v>1.1964</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4927</v>
+        <v>1.0434</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>0.153</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7237</v>
+        <v>-0.4097</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0464</v>
+        <v>-0.0519</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3227</v>
+        <v>-0.3578</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1751</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5157</v>
+        <v>0.3707</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0274</v>
+        <v>0.2716</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4883</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3904</v>
+        <v>-0.7395</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3207</v>
+        <v>0.5836</v>
       </c>
       <c r="E21" t="n">
-        <v>1.127</v>
+        <v>1.574</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4477</v>
+        <v>-0.9905</v>
       </c>
       <c r="G21" t="n">
         <v>3.632</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.168</v>
+        <v>-0.2638</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5516</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1745</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0822</v>
+        <v>-1.0514</v>
       </c>
       <c r="E22" t="n">
         <v>-1.0693</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="G22" t="n">
         <v>0.1338</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4419</v>
+        <v>-1.5421</v>
       </c>
       <c r="E23" t="n">
-        <v>3.5722</v>
+        <v>3.3487</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.0141</v>
+        <v>-4.8908</v>
       </c>
       <c r="G23" t="n">
         <v>0.4188</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3117</v>
+        <v>0.2115</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5396</v>
+        <v>0.316</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2278</v>
+        <v>-0.1046</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8249</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8358</v>
+        <v>-2.0028</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3186</v>
+        <v>-1.5421</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5172</v>
+        <v>-0.4607</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8991</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0633</v>
+        <v>-0.1036</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2023</v>
+        <v>-0.1457</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649999999999999</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.4621</v>
+        <v>8.207200000000002</v>
       </c>
       <c r="E25" t="n">
         <v>14.356</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.8937</v>
+        <v>-6.148899999999999</v>
       </c>
       <c r="G25" t="n">
         <v>8.443</v>
       </c>
       <c r="H25" t="n">
-        <v>5.884899999999999</v>
+        <v>5.8849</v>
       </c>
       <c r="I25" t="n">
         <v>2.5579</v>
@@ -2386,13 +2386,13 @@
         <v>7.2039</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.225000000000001</v>
+        <v>-9.225</v>
       </c>
       <c r="N25" t="n">
         <v>-4.579</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.645999999999999</v>
+        <v>-4.646</v>
       </c>
       <c r="P25" t="n">
         <v>3.2627</v>
@@ -2404,13 +2404,13 @@
         <v>15.2255</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9803</v>
+        <v>-2.2352</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2316</v>
+        <v>-1.2318</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7487</v>
+        <v>-1.0035</v>
       </c>
       <c r="V25" t="n">
         <v>-1.263</v>
